--- a/data/old_data/alex_zheng_20250130112211.xlsx
+++ b/data/old_data/alex_zheng_20250130112211.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexzheng/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/alexzheng/Developer/GitHub/EC331-project/data/old_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F795B91-8909-714F-95E9-CCBC77F6A87A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07FF9C1D-CF03-C14D-B357-FA0D121C7C62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17360" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
